--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/social_proof_display.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/social_proof_display.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>36.5</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>33.93</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.5</v>
+        <v>4.91</v>
       </c>
     </row>
   </sheetData>
